--- a/data/seed/portfolio/L-2024-4382/vypiska_2026-07_09.xlsx
+++ b/data/seed/portfolio/L-2024-4382/vypiska_2026-07_09.xlsx
@@ -423,7 +423,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J150"/>
+  <dimension ref="A1:J152"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -535,82 +535,82 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="n">
-        <v>46205</v>
+        <v>46204</v>
       </c>
       <c r="B8" t="n">
         <v>100</v>
       </c>
       <c r="C8" s="2" t="n"/>
       <c r="D8" s="2" t="n">
-        <v>4154000</v>
+        <v>35593000</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №6140 от 02.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за товар по с/ф №7827 от 01.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J8" s="2" t="n">
-        <v>286054000</v>
+        <v>317493000</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="n">
-        <v>46205</v>
+        <v>46206</v>
       </c>
       <c r="B9" t="n">
         <v>101</v>
       </c>
       <c r="C9" s="2" t="n"/>
       <c r="D9" s="2" t="n">
-        <v>2937000</v>
+        <v>15249000</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №124/26 от 02.07.2026</t>
+          <t>MAHSULOT UCHUN TO'LOV, SHARTNOMA №14/26, QQS 12%</t>
         </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>288991000</v>
+        <v>332742000</v>
       </c>
     </row>
     <row r="10">
@@ -620,37 +620,37 @@
       <c r="B10" t="n">
         <v>102</v>
       </c>
-      <c r="C10" s="2" t="n"/>
-      <c r="D10" s="2" t="n">
-        <v>18428000</v>
-      </c>
+      <c r="C10" s="2" t="n">
+        <v>8391000</v>
+      </c>
+      <c r="D10" s="2" t="n"/>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Saodat Metall MChJ</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>204023835</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000536219768001</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9034 за поставленный товар</t>
+          <t>Tovarlar uchun to'lov h/f №2078</t>
         </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>307419000</v>
+        <v>324351000</v>
       </c>
     </row>
     <row r="11">
@@ -661,22 +661,22 @@
         <v>103</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>28309000</v>
+        <v>10952000</v>
       </c>
       <c r="D11" s="2" t="n"/>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Samarqand Sut Mahsulotlari MChJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>346550012</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>20208000972500892001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -686,11 +686,11 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАРЫ СОГЛАСНО С/Ф №9985</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №156/26</t>
         </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>279110000</v>
+        <v>313399000</v>
       </c>
     </row>
     <row r="12">
@@ -702,35 +702,35 @@
       </c>
       <c r="C12" s="2" t="n"/>
       <c r="D12" s="2" t="n">
-        <v>20282000</v>
+        <v>38972000</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Chust Mebel AJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>376006589</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>20208000497660944001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №53/26, QQS 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №134/26, QQS 12%</t>
         </is>
       </c>
       <c r="J12" s="2" t="n">
-        <v>299392000</v>
+        <v>352371000</v>
       </c>
     </row>
     <row r="13">
@@ -742,35 +742,35 @@
       </c>
       <c r="C13" s="2" t="n"/>
       <c r="D13" s="2" t="n">
-        <v>13936000</v>
+        <v>19225000</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №5851 от 06.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №147/26, QQS 12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>313328000</v>
+        <v>371596000</v>
       </c>
     </row>
     <row r="14">
@@ -782,21 +782,21 @@
       </c>
       <c r="C14" s="2" t="n"/>
       <c r="D14" s="2" t="n">
-        <v>7856000</v>
+        <v>12640000</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Yulduz Dori-Darmon MChJ</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>355529082</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000920315719001</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -806,11 +806,11 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ТОВАР ПО С/Ф №6927 ОТ 06.07.2026, В Т.Ч. НДС 12%</t>
+          <t>Предоплата за товар по дог. №99/26 от 06.07.2026</t>
         </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>321184000</v>
+        <v>384236000</v>
       </c>
     </row>
     <row r="15">
@@ -822,35 +822,35 @@
       </c>
       <c r="C15" s="2" t="n"/>
       <c r="D15" s="2" t="n">
-        <v>6187000</v>
+        <v>11804000</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №101/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №8683</t>
         </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>327371000</v>
+        <v>396040000</v>
       </c>
     </row>
     <row r="16">
@@ -862,35 +862,35 @@
       </c>
       <c r="C16" s="2" t="n"/>
       <c r="D16" s="2" t="n">
-        <v>3364000</v>
+        <v>3609000</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>Shartnoma №60/26 bo'yicha oldindan to'lov</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7312</t>
         </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>330735000</v>
+        <v>399649000</v>
       </c>
     </row>
     <row r="17">
@@ -901,412 +901,417 @@
         <v>109</v>
       </c>
       <c r="C17" s="2" t="n">
-        <v>37167000</v>
+        <v>8111000</v>
       </c>
       <c r="D17" s="2" t="n"/>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Saodat Metall MChJ</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>204023835</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000536219768001</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>Ish haqi to'lovi iyun 2026 (plastik kartalarga)</t>
+          <t>Xom ashyo uchun to'lov, shartn. №262/26, QQS bilan</t>
         </is>
       </c>
       <c r="J17" s="2" t="n">
-        <v>293568000</v>
+        <v>391538000</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B18" t="n">
         <v>110</v>
       </c>
-      <c r="C18" s="2" t="n"/>
-      <c r="D18" s="2" t="n">
-        <v>137262000</v>
-      </c>
+      <c r="C18" s="2" t="n">
+        <v>10468000</v>
+      </c>
+      <c r="D18" s="2" t="n"/>
       <c r="E18" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Saodat Metall MChJ</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>204023835</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000536219768001</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №224/26, QQS 12%</t>
+          <t>Оплата за упаковочные материалы, с/ф №4847</t>
         </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>430830000</v>
+        <v>381070000</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="3" t="n">
-        <v>46210</v>
+        <v>46209</v>
       </c>
       <c r="B19" t="n">
         <v>111</v>
       </c>
-      <c r="C19" s="2" t="n"/>
-      <c r="D19" s="2" t="n">
-        <v>5220000</v>
-      </c>
+      <c r="C19" s="2" t="n">
+        <v>18873000</v>
+      </c>
+      <c r="D19" s="2" t="n"/>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Shahrisabz Qurilish Materiallari MChJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>290625514</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>20208000216803594001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №286/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №3/26</t>
         </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>436050000</v>
+        <v>362197000</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="3" t="n">
-        <v>46211</v>
+        <v>46209</v>
       </c>
       <c r="B20" t="n">
         <v>112</v>
       </c>
       <c r="C20" s="2" t="n">
-        <v>17184000</v>
+        <v>37167000</v>
       </c>
       <c r="D20" s="2" t="n"/>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>228897103</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №4919</t>
+          <t>Iyun oyi uchun ish haqi, reestr №2316</t>
         </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>418866000</v>
+        <v>325030000</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="n">
-        <v>46212</v>
+        <v>46209</v>
       </c>
       <c r="B21" t="n">
         <v>113</v>
       </c>
-      <c r="C21" s="2" t="n"/>
-      <c r="D21" s="2" t="n">
-        <v>7029000</v>
-      </c>
+      <c r="C21" s="2" t="n">
+        <v>130463000</v>
+      </c>
+      <c r="D21" s="2" t="n"/>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Qo'qon Savdo MChJ</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>270913111</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000715704672001</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №233/26, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №1220</t>
         </is>
       </c>
       <c r="J21" s="2" t="n">
-        <v>425895000</v>
+        <v>194567000</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="3" t="n">
-        <v>46212</v>
+        <v>46210</v>
       </c>
       <c r="B22" t="n">
         <v>114</v>
       </c>
-      <c r="C22" s="2" t="n"/>
-      <c r="D22" s="2" t="n">
-        <v>2943000</v>
-      </c>
+      <c r="C22" s="2" t="n">
+        <v>11529000</v>
+      </c>
+      <c r="D22" s="2" t="n"/>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Chust Mebel AJ</t>
+          <t>Marg'ilon Avto Savdo MChJ</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>376006589</t>
+          <t>213792773</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>20208000497660944001</t>
+          <t>20208000833128138001</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00987</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>ОПЛАТА ПО СЧЕТ-ФАКТУРЕ №6198 ЗА ПОСТАВЛЕННЫЙ ТОВАР</t>
+          <t>Оплата за товары согласно счет-фактуре №9966</t>
         </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>428838000</v>
+        <v>183038000</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B23" t="n">
         <v>115</v>
       </c>
-      <c r="C23" s="2" t="n">
-        <v>3891000</v>
-      </c>
-      <c r="D23" s="2" t="n"/>
+      <c r="C23" s="2" t="n"/>
+      <c r="D23" s="2" t="n">
+        <v>9160000</v>
+      </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Urganch Qurilish Materiallari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>279508176</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>20208000985398076001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>Ijara haqi iyul oyi uchun, shartnoma №77/21</t>
+          <t>Mahsulot uchun to'lov, shartnoma №196/26, QQS 12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>424947000</v>
+        <v>192198000</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="n">
-        <v>46212</v>
+        <v>46211</v>
       </c>
       <c r="B24" t="n">
         <v>116</v>
       </c>
-      <c r="C24" s="2" t="n">
-        <v>19626000</v>
-      </c>
-      <c r="D24" s="2" t="n"/>
+      <c r="C24" s="2" t="n"/>
+      <c r="D24" s="2" t="n">
+        <v>5931000</v>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Bahor Logistik AJ</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>262551432</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000680359481001</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №282/26</t>
+          <t>Tovar uchun to'lov, h/f №283 08.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>405321000</v>
+        <v>198129000</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B25" t="n">
         <v>117</v>
       </c>
       <c r="C25" s="2" t="n"/>
       <c r="D25" s="2" t="n">
-        <v>29025000</v>
+        <v>4810000</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Xiva Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>300658994</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000766094413001</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №230/26 ОТ 10.07.2026</t>
+          <t>Оплата за товар по счет-фактуре №7039 от 08.07.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>434346000</v>
+        <v>202939000</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B26" t="n">
         <v>118</v>
       </c>
       <c r="C26" s="2" t="n">
-        <v>59919000</v>
+        <v>3891000</v>
       </c>
       <c r="D26" s="2" t="n"/>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Marg'ilon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>294343295</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000792958688001</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №6773</t>
+          <t>Bino ijarasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>374427000</v>
+        <v>199048000</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="3" t="n">
-        <v>46213</v>
+        <v>46211</v>
       </c>
       <c r="B27" t="n">
         <v>119</v>
       </c>
       <c r="C27" s="2" t="n">
-        <v>66600000</v>
+        <v>6261000</v>
       </c>
       <c r="D27" s="2" t="n"/>
       <c r="E27" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-4382)</t>
+          <t>Bahor Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>16307000371475974417</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -1316,117 +1321,112 @@
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-4382 bo'yicha navbatdagi to'lov (07.2026)</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №20/26</t>
         </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>307827000</v>
+        <v>192787000</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B28" t="n">
         <v>120</v>
       </c>
       <c r="C28" s="2" t="n"/>
       <c r="D28" s="2" t="n">
-        <v>58551000</v>
+        <v>11003000</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Olmaliq Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>285833812</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000209807425001</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №3320 за поставленный товар</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №4213</t>
         </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>366378000</v>
+        <v>203790000</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B29" t="n">
         <v>121</v>
       </c>
       <c r="C29" s="2" t="n"/>
       <c r="D29" s="2" t="n">
-        <v>33914000</v>
+        <v>3831000</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2945 от 13.07.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7605</t>
         </is>
       </c>
       <c r="J29" s="2" t="n">
-        <v>400292000</v>
+        <v>207621000</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="3" t="n">
-        <v>46216</v>
+        <v>46213</v>
       </c>
       <c r="B30" t="n">
         <v>122</v>
       </c>
-      <c r="C30" s="2" t="n"/>
-      <c r="D30" s="2" t="n">
-        <v>5293000</v>
-      </c>
+      <c r="C30" s="2" t="n">
+        <v>66600000</v>
+      </c>
+      <c r="D30" s="2" t="n"/>
       <c r="E30" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>206716469</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-4382)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>16307000371475974417</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -1436,437 +1436,437 @@
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №4060 13.07.2026, QQS bilan</t>
+          <t>Kredit shartnomasi L-2024-4382 bo'yicha navbatdagi to'lov (07.2026)</t>
         </is>
       </c>
       <c r="J30" s="2" t="n">
-        <v>405585000</v>
+        <v>141021000</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="n">
-        <v>46216</v>
+        <v>46217</v>
       </c>
       <c r="B31" t="n">
         <v>123</v>
       </c>
-      <c r="C31" s="2" t="n"/>
-      <c r="D31" s="2" t="n">
-        <v>4989000</v>
-      </c>
+      <c r="C31" s="2" t="n">
+        <v>31989000</v>
+      </c>
+      <c r="D31" s="2" t="n"/>
       <c r="E31" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Urganch Moy MChJ</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>380892181</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000223286429001</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №5979 за поставленный товар</t>
+          <t>Materiallar uchun oldinan to'lov, shartnoma №283/26</t>
         </is>
       </c>
       <c r="J31" s="2" t="n">
-        <v>410574000</v>
+        <v>109032000</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B32" t="n">
         <v>124</v>
       </c>
-      <c r="C32" s="2" t="n"/>
-      <c r="D32" s="2" t="n">
-        <v>4623000</v>
-      </c>
+      <c r="C32" s="2" t="n">
+        <v>5068000</v>
+      </c>
+      <c r="D32" s="2" t="n"/>
       <c r="E32" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №258/26, НДС 12%</t>
+          <t>Iyun oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J32" s="2" t="n">
-        <v>415197000</v>
+        <v>103964000</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="n">
-        <v>46216</v>
+        <v>46218</v>
       </c>
       <c r="B33" t="n">
         <v>125</v>
       </c>
-      <c r="C33" s="2" t="n"/>
-      <c r="D33" s="2" t="n">
-        <v>3171000</v>
-      </c>
+      <c r="C33" s="2" t="n">
+        <v>5068000</v>
+      </c>
+      <c r="D33" s="2" t="n"/>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Shahrisabz Qurilish Materiallari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>290625514</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>20208000216803594001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №250/26, НДС 12%</t>
+          <t>Jismoniy shaxslar daromad solig'i iyun 2026</t>
         </is>
       </c>
       <c r="J33" s="2" t="n">
-        <v>418368000</v>
+        <v>98896000</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="n">
-        <v>46216</v>
+        <v>46223</v>
       </c>
       <c r="B34" t="n">
         <v>126</v>
       </c>
-      <c r="C34" s="2" t="n">
-        <v>20501000</v>
-      </c>
-      <c r="D34" s="2" t="n"/>
+      <c r="C34" s="2" t="n"/>
+      <c r="D34" s="2" t="n">
+        <v>9395000</v>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Qo'qon Trans Servis MChJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>363663248</t>
+          <t>398766839</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>20208000121414043001</t>
+          <t>20208000499303116001</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №7181</t>
+          <t>Предоплата за товар по дог. №38/26 от 20.07.2026</t>
         </is>
       </c>
       <c r="J34" s="2" t="n">
-        <v>397867000</v>
+        <v>108291000</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B35" t="n">
         <v>127</v>
       </c>
       <c r="C35" s="2" t="n"/>
       <c r="D35" s="2" t="n">
-        <v>3212000</v>
+        <v>3520000</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Shahrisabz Qurilish Materiallari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>290625514</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>20208000216803594001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №9495 от 14.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №188/26, QQS 12%</t>
         </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>401079000</v>
+        <v>111811000</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="n">
-        <v>46217</v>
+        <v>46223</v>
       </c>
       <c r="B36" t="n">
         <v>128</v>
       </c>
-      <c r="C36" s="2" t="n"/>
-      <c r="D36" s="2" t="n">
-        <v>2993000</v>
-      </c>
+      <c r="C36" s="2" t="n">
+        <v>42415000</v>
+      </c>
+      <c r="D36" s="2" t="n"/>
       <c r="E36" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2331</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №110/26, QQS bilan</t>
         </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>404072000</v>
+        <v>69396000</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="n">
-        <v>46218</v>
+        <v>46224</v>
       </c>
       <c r="B37" t="n">
         <v>129</v>
       </c>
       <c r="C37" s="2" t="n"/>
       <c r="D37" s="2" t="n">
-        <v>16461000</v>
+        <v>43698000</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №3944 от 15.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №158/26, QQS 12%</t>
         </is>
       </c>
       <c r="J37" s="2" t="n">
-        <v>420533000</v>
+        <v>113094000</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B38" t="n">
         <v>130</v>
       </c>
-      <c r="C38" s="2" t="n">
-        <v>5068000</v>
-      </c>
-      <c r="D38" s="2" t="n"/>
+      <c r="C38" s="2" t="n"/>
+      <c r="D38" s="2" t="n">
+        <v>26467000</v>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>Уплата социального налога за июнь</t>
+          <t>Предоплата за товар по договору №281/26 от 21.07.2026</t>
         </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>415465000</v>
+        <v>139561000</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="n">
-        <v>46219</v>
+        <v>46224</v>
       </c>
       <c r="B39" t="n">
         <v>131</v>
       </c>
-      <c r="C39" s="2" t="n">
-        <v>5068000</v>
-      </c>
-      <c r="D39" s="2" t="n"/>
+      <c r="C39" s="2" t="n"/>
+      <c r="D39" s="2" t="n">
+        <v>5520000</v>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>JShDS iyun oyi uchun</t>
+          <t>Mahsulot uchun to'lov, shartnoma №50/26, QQS 12%</t>
         </is>
       </c>
       <c r="J39" s="2" t="n">
-        <v>410397000</v>
+        <v>145081000</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="n">
-        <v>46220</v>
+        <v>46224</v>
       </c>
       <c r="B40" t="n">
         <v>132</v>
       </c>
-      <c r="C40" s="2" t="n"/>
-      <c r="D40" s="2" t="n">
-        <v>11640000</v>
-      </c>
+      <c r="C40" s="2" t="n">
+        <v>6295000</v>
+      </c>
+      <c r="D40" s="2" t="n"/>
       <c r="E40" t="inlineStr">
         <is>
-          <t>Farg'ona Un Mahsulotlari MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>329555290</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>20208000219203157001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №255/26, НДС 12%</t>
+          <t>Qo'shilgan qiymat solig'i iyun oyi</t>
         </is>
       </c>
       <c r="J40" s="2" t="n">
-        <v>422037000</v>
+        <v>138786000</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="n">
-        <v>46220</v>
+        <v>46225</v>
       </c>
       <c r="B41" t="n">
         <v>133</v>
       </c>
-      <c r="C41" s="2" t="n"/>
-      <c r="D41" s="2" t="n">
-        <v>3976000</v>
-      </c>
+      <c r="C41" s="2" t="n">
+        <v>97409000</v>
+      </c>
+      <c r="D41" s="2" t="n"/>
       <c r="E41" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
@@ -1876,37 +1876,37 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №12/26, НДС 12%</t>
+          <t>Оплата за товары согласно с/ф №3185</t>
         </is>
       </c>
       <c r="J41" s="2" t="n">
-        <v>426013000</v>
+        <v>41377000</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B42" t="n">
         <v>134</v>
       </c>
       <c r="C42" s="2" t="n"/>
       <c r="D42" s="2" t="n">
-        <v>5183000</v>
+        <v>36111000</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
@@ -1916,317 +1916,317 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА ПРОДУКЦИЮ ПО ДОГОВОРУ №158/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1485</t>
         </is>
       </c>
       <c r="J42" s="2" t="n">
-        <v>431196000</v>
+        <v>77488000</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B43" t="n">
         <v>135</v>
       </c>
       <c r="C43" s="2" t="n"/>
       <c r="D43" s="2" t="n">
-        <v>3350000</v>
+        <v>9113000</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Xiva Oziq-ovqat Savdo XK</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>300658994</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000766094413001</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №805 от 20.07.2026, в т.ч. НДС 12%</t>
+          <t>Оплата по счет-фактуре №2174 за поставленный товар</t>
         </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>434546000</v>
+        <v>86601000</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="n">
-        <v>46223</v>
+        <v>46226</v>
       </c>
       <c r="B44" t="n">
         <v>136</v>
       </c>
-      <c r="C44" s="2" t="n">
-        <v>19975000</v>
-      </c>
-      <c r="D44" s="2" t="n"/>
+      <c r="C44" s="2" t="n"/>
+      <c r="D44" s="2" t="n">
+        <v>4269000</v>
+      </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №180/26</t>
+          <t>Tovar uchun to'lov, h/f №7778 23.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>414571000</v>
+        <v>90870000</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="n">
-        <v>46225</v>
+        <v>46226</v>
       </c>
       <c r="B45" t="n">
         <v>137</v>
       </c>
-      <c r="C45" s="2" t="n"/>
-      <c r="D45" s="2" t="n">
-        <v>54444000</v>
-      </c>
+      <c r="C45" s="2" t="n">
+        <v>2432000</v>
+      </c>
+      <c r="D45" s="2" t="n"/>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Chust Mebel AJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>376006589</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>20208000497660944001</t>
+          <t>20208000941079278001</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дговору №291/26, НДС 12%</t>
+          <t>Elektr energiyasi uchun to'lov iyul</t>
         </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>469015000</v>
+        <v>88438000</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="n">
-        <v>46225</v>
+        <v>46227</v>
       </c>
       <c r="B46" t="n">
         <v>138</v>
       </c>
-      <c r="C46" s="2" t="n">
-        <v>6388000</v>
-      </c>
-      <c r="D46" s="2" t="n"/>
+      <c r="C46" s="2" t="n"/>
+      <c r="D46" s="2" t="n">
+        <v>19641000</v>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>НДС за июнь 2026 г.</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №7274 24.07.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J46" s="2" t="n">
-        <v>462627000</v>
+        <v>108079000</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B47" t="n">
         <v>139</v>
       </c>
       <c r="C47" s="2" t="n"/>
       <c r="D47" s="2" t="n">
-        <v>11081000</v>
+        <v>28837000</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>Yangi Hayot Moy MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>355987668</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>20208000904993031001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №8991 от 23.07.2026, в т.ч. НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9178 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>473708000</v>
+        <v>136916000</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B48" t="n">
         <v>140</v>
       </c>
       <c r="C48" s="2" t="n"/>
       <c r="D48" s="2" t="n">
-        <v>5111000</v>
+        <v>14133000</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №3928 от 23.07.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartnoma №187/26, QQS 12%</t>
         </is>
       </c>
       <c r="J48" s="2" t="n">
-        <v>478819000</v>
+        <v>151049000</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B49" t="n">
         <v>141</v>
       </c>
       <c r="C49" s="2" t="n"/>
       <c r="D49" s="2" t="n">
-        <v>2718000</v>
+        <v>9975000</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №1251 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3047 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>481537000</v>
+        <v>161024000</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="n">
-        <v>46226</v>
+        <v>46230</v>
       </c>
       <c r="B50" t="n">
         <v>142</v>
       </c>
-      <c r="C50" s="2" t="n">
-        <v>29621000</v>
-      </c>
-      <c r="D50" s="2" t="n"/>
+      <c r="C50" s="2" t="n"/>
+      <c r="D50" s="2" t="n">
+        <v>9261000</v>
+      </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Samarqand Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>346550012</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>20208000972500892001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2236,11 +2236,11 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>Оплата за сырье по дог. №30/26 от 23.07.2026, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №721</t>
         </is>
       </c>
       <c r="J50" s="2" t="n">
-        <v>451916000</v>
+        <v>170285000</v>
       </c>
     </row>
     <row r="51">
@@ -2250,37 +2250,37 @@
       <c r="B51" t="n">
         <v>143</v>
       </c>
-      <c r="C51" s="2" t="n">
-        <v>2432000</v>
-      </c>
-      <c r="D51" s="2" t="n"/>
+      <c r="C51" s="2" t="n"/>
+      <c r="D51" s="2" t="n">
+        <v>3980000</v>
+      </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>20208000028978953001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию за июль 2026 г.</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5279 27.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>449484000</v>
+        <v>174265000</v>
       </c>
     </row>
     <row r="52">
@@ -2291,102 +2291,102 @@
         <v>144</v>
       </c>
       <c r="C52" s="2" t="n">
-        <v>154761000</v>
+        <v>14794000</v>
       </c>
       <c r="D52" s="2" t="n"/>
       <c r="E52" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно счет-фактуре №4180</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №175/26</t>
         </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>294723000</v>
+        <v>159471000</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="n">
-        <v>46231</v>
+        <v>46232</v>
       </c>
       <c r="B53" t="n">
         <v>145</v>
       </c>
       <c r="C53" s="2" t="n"/>
       <c r="D53" s="2" t="n">
-        <v>10821000</v>
+        <v>32405000</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>Yangi Hayot Moy MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>355987668</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>20208000904993031001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №2334</t>
+          <t>Shartnoma №261/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>305544000</v>
+        <v>191876000</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="n">
-        <v>46231</v>
+        <v>46233</v>
       </c>
       <c r="B54" t="n">
         <v>146</v>
       </c>
       <c r="C54" s="2" t="n"/>
       <c r="D54" s="2" t="n">
-        <v>5091000</v>
+        <v>53372000</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -2396,232 +2396,232 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №94/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2677</t>
         </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>310635000</v>
+        <v>245248000</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B55" t="n">
         <v>147</v>
       </c>
       <c r="C55" s="2" t="n"/>
       <c r="D55" s="2" t="n">
-        <v>10592000</v>
+        <v>43020000</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>Chust Mebel AJ</t>
+          <t>Olmaliq Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>376006589</t>
+          <t>285833812</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>20208000497660944001</t>
+          <t>20208000209807425001</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА ТОВАР ПО ДОГОВОРУ №246/26 ОТ 29.07.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №8581 31.07.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>321227000</v>
+        <v>288268000</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="n">
-        <v>46232</v>
+        <v>46234</v>
       </c>
       <c r="B56" t="n">
         <v>148</v>
       </c>
       <c r="C56" s="2" t="n">
-        <v>41226000</v>
+        <v>300000</v>
       </c>
       <c r="D56" s="2" t="n"/>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F56" t="inlineStr">
-        <is>
-          <t>228897103</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №36/26</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J56" s="2" t="n">
-        <v>280001000</v>
+        <v>287968000</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B57" t="n">
         <v>149</v>
       </c>
       <c r="C57" s="2" t="n"/>
       <c r="D57" s="2" t="n">
-        <v>13415000</v>
+        <v>8896000</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №275/26 от 30.07.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1122 03.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>293416000</v>
+        <v>296864000</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B58" t="n">
         <v>150</v>
       </c>
       <c r="C58" s="2" t="n"/>
       <c r="D58" s="2" t="n">
-        <v>3093000</v>
+        <v>6984000</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Shahrisabz Qurilish Materiallari MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>290625514</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>20208000216803594001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5508</t>
+          <t>Shartnoma №80/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>296509000</v>
+        <v>303848000</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="n">
-        <v>46233</v>
+        <v>46237</v>
       </c>
       <c r="B59" t="n">
         <v>151</v>
       </c>
-      <c r="C59" s="2" t="n">
-        <v>17187000</v>
-      </c>
-      <c r="D59" s="2" t="n"/>
+      <c r="C59" s="2" t="n"/>
+      <c r="D59" s="2" t="n">
+        <v>4521000</v>
+      </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Bahor Logistik AJ</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>262551432</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000680359481001</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>Оплата за транспортне услуги по договору №81/26</t>
+          <t>Shartnoma №79/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J59" s="2" t="n">
-        <v>279322000</v>
+        <v>308369000</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="n">
-        <v>46234</v>
+        <v>46237</v>
       </c>
       <c r="B60" t="n">
         <v>152</v>
       </c>
-      <c r="C60" s="2" t="n">
-        <v>300000</v>
-      </c>
-      <c r="D60" s="2" t="n"/>
+      <c r="C60" s="2" t="n"/>
+      <c r="D60" s="2" t="n">
+        <v>3004000</v>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
@@ -2631,11 +2631,11 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>Hisob-kassa xizmati uchun haq</t>
+          <t>Tovar uchun to'lov, hisob-faktura №1416 03.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>279022000</v>
+        <v>311373000</v>
       </c>
     </row>
     <row r="61">
@@ -2645,37 +2645,37 @@
       <c r="B61" t="n">
         <v>153</v>
       </c>
-      <c r="C61" s="2" t="n"/>
-      <c r="D61" s="2" t="n">
-        <v>17215000</v>
-      </c>
+      <c r="C61" s="2" t="n">
+        <v>4990000</v>
+      </c>
+      <c r="D61" s="2" t="n"/>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Saodat Metall MChJ</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>204023835</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000536219768001</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №8636 от 03.08.2026, в т.ч. НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №295/26</t>
         </is>
       </c>
       <c r="J61" s="2" t="n">
-        <v>296237000</v>
+        <v>306383000</v>
       </c>
     </row>
     <row r="62">
@@ -2686,22 +2686,22 @@
         <v>154</v>
       </c>
       <c r="C62" s="2" t="n">
-        <v>7569000</v>
+        <v>9293000</v>
       </c>
       <c r="D62" s="2" t="n"/>
       <c r="E62" t="inlineStr">
         <is>
-          <t>Samarqand Sut Mahsulotlari MChJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>346550012</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>20208000972500892001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2711,37 +2711,32 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №55/26</t>
+          <t>Xom ashyo uchun to'lov, shartn. №7/26, QQS bilan</t>
         </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>288668000</v>
+        <v>297090000</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="n">
-        <v>46237</v>
+        <v>46238</v>
       </c>
       <c r="B63" t="n">
         <v>155</v>
       </c>
       <c r="C63" s="2" t="n">
-        <v>13141000</v>
+        <v>33403000</v>
       </c>
       <c r="D63" s="2" t="n"/>
       <c r="E63" t="inlineStr">
         <is>
-          <t>Samarqand Sut Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>346550012</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>20208000972500892001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
@@ -2751,112 +2746,117 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №287/26</t>
+          <t>Iyul oyi uchun ish haqi, reestr №7114</t>
         </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>275527000</v>
+        <v>263687000</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="3" t="n">
-        <v>46237</v>
+        <v>46239</v>
       </c>
       <c r="B64" t="n">
         <v>156</v>
       </c>
-      <c r="C64" s="2" t="n">
-        <v>215670000</v>
-      </c>
-      <c r="D64" s="2" t="n"/>
+      <c r="C64" s="2" t="n"/>
+      <c r="D64" s="2" t="n">
+        <v>4265000</v>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>Xom ashyo uchun to'lov, shartnoma №233/26, QQS bilan</t>
+          <t>Оплата за товар по счет-фактуре №1051 от 05.08.2026, в т.ч. НДС 12%</t>
         </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>59857000</v>
+        <v>267952000</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="n">
-        <v>46238</v>
+        <v>46239</v>
       </c>
       <c r="B65" t="n">
         <v>157</v>
       </c>
-      <c r="C65" s="2" t="n"/>
-      <c r="D65" s="2" t="n">
-        <v>4849000</v>
-      </c>
+      <c r="C65" s="2" t="n">
+        <v>5325000</v>
+      </c>
+      <c r="D65" s="2" t="n"/>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Saodat Metall MChJ</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>204023835</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000536219768001</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №257/26, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartn. №287/26, QQS bilan</t>
         </is>
       </c>
       <c r="J65" s="2" t="n">
-        <v>64706000</v>
+        <v>262627000</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B66" t="n">
         <v>158</v>
       </c>
-      <c r="C66" s="2" t="n">
-        <v>33403000</v>
-      </c>
-      <c r="D66" s="2" t="n"/>
+      <c r="C66" s="2" t="n"/>
+      <c r="D66" s="2" t="n">
+        <v>3394000</v>
+      </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
@@ -2866,176 +2866,176 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за июль 2026 г. согласно реестру №9823</t>
+          <t>Tovar uchun to'lov, hisob-faktura №7119 06.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>31303000</v>
+        <v>266021000</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="3" t="n">
-        <v>46238</v>
+        <v>46240</v>
       </c>
       <c r="B67" t="n">
         <v>159</v>
       </c>
       <c r="C67" s="2" t="n">
-        <v>35096000</v>
+        <v>11053000</v>
       </c>
       <c r="D67" s="2" t="n"/>
       <c r="E67" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>ОПЛАТА ЗА СЫРЬЕ ПО ДОГОВОРУ №185/26 ОТ 04.08.2026, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №176/26, QQS bilan</t>
         </is>
       </c>
       <c r="J67" s="2" t="n">
-        <v>-3793000</v>
+        <v>254968000</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B68" t="n">
         <v>160</v>
       </c>
       <c r="C68" s="2" t="n"/>
       <c r="D68" s="2" t="n">
-        <v>44325000</v>
+        <v>4987000</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>Yangi Hayot Moy MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>355987668</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>20208000904993031001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №345 от 05.08.2026, в т.ч. НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2934</t>
         </is>
       </c>
       <c r="J68" s="2" t="n">
-        <v>40532000</v>
+        <v>259955000</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="n">
-        <v>46239</v>
+        <v>46241</v>
       </c>
       <c r="B69" t="n">
         <v>161</v>
       </c>
       <c r="C69" s="2" t="n">
-        <v>6554000</v>
+        <v>9463000</v>
       </c>
       <c r="D69" s="2" t="n"/>
       <c r="E69" t="inlineStr">
         <is>
-          <t>Chirchiq Logistik AJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>232709131</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>20208000157157046001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №276/26</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №181/26</t>
         </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>33978000</v>
+        <v>250492000</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B70" t="n">
         <v>162</v>
       </c>
       <c r="C70" s="2" t="n"/>
       <c r="D70" s="2" t="n">
-        <v>10992000</v>
+        <v>221613000</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Shahrisabz Qurilish Materiallari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>290625514</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>20208000216803594001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №7962 за поставленный товар</t>
+          <t>Mahsulot uchun to'lov, shartnoma №109/26, QQS 12%</t>
         </is>
       </c>
       <c r="J70" s="2" t="n">
-        <v>44970000</v>
+        <v>472105000</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="n">
-        <v>46241</v>
+        <v>46244</v>
       </c>
       <c r="B71" t="n">
         <v>163</v>
@@ -3046,31 +3046,31 @@
       <c r="D71" s="2" t="n"/>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Urganch Qurilish Materiallari MChJ</t>
+          <t>Marg'ilon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>279508176</t>
+          <t>294343295</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>20208000985398076001</t>
+          <t>20208000792958688001</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>Аренда помещения за август, дог. №77/21</t>
+          <t>Bino ijarasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J71" s="2" t="n">
-        <v>41473000</v>
+        <v>468608000</v>
       </c>
     </row>
     <row r="72">
@@ -3080,37 +3080,37 @@
       <c r="B72" t="n">
         <v>164</v>
       </c>
-      <c r="C72" s="2" t="n"/>
-      <c r="D72" s="2" t="n">
-        <v>58751000</v>
-      </c>
+      <c r="C72" s="2" t="n">
+        <v>6001000</v>
+      </c>
+      <c r="D72" s="2" t="n"/>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Urganch Moy MChJ</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>380892181</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000223286429001</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №85/26 от 10.08.2026</t>
+          <t>Tovarlar uchun to'lov h/f №9399</t>
         </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>100224000</v>
+        <v>462607000</v>
       </c>
     </row>
     <row r="73">
@@ -3120,37 +3120,37 @@
       <c r="B73" t="n">
         <v>165</v>
       </c>
-      <c r="C73" s="2" t="n"/>
-      <c r="D73" s="2" t="n">
-        <v>11756000</v>
-      </c>
+      <c r="C73" s="2" t="n">
+        <v>18055000</v>
+      </c>
+      <c r="D73" s="2" t="n"/>
       <c r="E73" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №267/26, НДС 12%</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №142/26, QQS bilan</t>
         </is>
       </c>
       <c r="J73" s="2" t="n">
-        <v>111980000</v>
+        <v>444552000</v>
       </c>
     </row>
     <row r="74">
@@ -3185,193 +3185,193 @@
         </is>
       </c>
       <c r="J74" s="2" t="n">
-        <v>45380000</v>
+        <v>377952000</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="3" t="n">
-        <v>46245</v>
+        <v>46247</v>
       </c>
       <c r="B75" t="n">
         <v>167</v>
       </c>
-      <c r="C75" s="2" t="n"/>
-      <c r="D75" s="2" t="n">
-        <v>12834000</v>
-      </c>
+      <c r="C75" s="2" t="n">
+        <v>61711000</v>
+      </c>
+      <c r="D75" s="2" t="n"/>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Saodat Metall MChJ</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>204023835</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000536219768001</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>Оплаа за продукцию по договору №150/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartn. №165/26</t>
         </is>
       </c>
       <c r="J75" s="2" t="n">
-        <v>58214000</v>
+        <v>316241000</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="3" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="B76" t="n">
         <v>168</v>
       </c>
       <c r="C76" s="2" t="n"/>
       <c r="D76" s="2" t="n">
-        <v>10643000</v>
+        <v>4537000</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>Chust Mebel AJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>376006589</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>20208000497660944001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2130 от 11.08.2026, в т.ч. НДС 12%</t>
+          <t>TOVAR UCHUN TO'LOV, HISOB-FAKTURA №4197 14.08.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J76" s="2" t="n">
-        <v>68857000</v>
+        <v>320778000</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="B77" t="n">
         <v>169</v>
       </c>
-      <c r="C77" s="2" t="n"/>
-      <c r="D77" s="2" t="n">
-        <v>5275000</v>
-      </c>
+      <c r="C77" s="2" t="n">
+        <v>5336000</v>
+      </c>
+      <c r="D77" s="2" t="n"/>
       <c r="E77" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Urganch Moy MChJ</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>380892181</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000223286429001</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №10/26, НДС 12%</t>
+          <t>Оплата за товары согласно счет-фактуре №1452</t>
         </is>
       </c>
       <c r="J77" s="2" t="n">
-        <v>74132000</v>
+        <v>315442000</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B78" t="n">
         <v>170</v>
       </c>
       <c r="C78" s="2" t="n"/>
       <c r="D78" s="2" t="n">
-        <v>25797000</v>
+        <v>40628000</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №966 от 12.08.2026, в т.ч. НДС 12%</t>
+          <t>Предоплата за товар по договору №205/26 от 17.08.2026</t>
         </is>
       </c>
       <c r="J78" s="2" t="n">
-        <v>99929000</v>
+        <v>356070000</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="3" t="n">
-        <v>46246</v>
+        <v>46251</v>
       </c>
       <c r="B79" t="n">
         <v>171</v>
       </c>
       <c r="C79" s="2" t="n"/>
       <c r="D79" s="2" t="n">
-        <v>16459000</v>
+        <v>7357000</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3381,56 +3381,56 @@
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №5865 за поставленный товар</t>
+          <t>Оплата за продукцию по договору №80/26, НДС 12%</t>
         </is>
       </c>
       <c r="J79" s="2" t="n">
-        <v>116388000</v>
+        <v>363427000</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="3" t="n">
-        <v>46247</v>
+        <v>46251</v>
       </c>
       <c r="B80" t="n">
         <v>172</v>
       </c>
       <c r="C80" s="2" t="n"/>
       <c r="D80" s="2" t="n">
-        <v>4989000</v>
+        <v>6006000</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №25/26 от 13.08.2026</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №2313</t>
         </is>
       </c>
       <c r="J80" s="2" t="n">
-        <v>121377000</v>
+        <v>369433000</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B81" t="n">
         <v>173</v>
@@ -3461,16 +3461,16 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>Социальный налог за июль 2026 г.</t>
+          <t>Iyul oyi uchun ijtimoiy soliq</t>
         </is>
       </c>
       <c r="J81" s="2" t="n">
-        <v>116822000</v>
+        <v>364878000</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B82" t="n">
         <v>174</v>
@@ -3501,77 +3501,77 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за июль 2026 г.</t>
+          <t>JShDS iyul oyi uchun</t>
         </is>
       </c>
       <c r="J82" s="2" t="n">
-        <v>112267000</v>
+        <v>360323000</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="3" t="n">
-        <v>46248</v>
+        <v>46251</v>
       </c>
       <c r="B83" t="n">
         <v>175</v>
       </c>
       <c r="C83" s="2" t="n">
-        <v>30625000</v>
+        <v>148207000</v>
       </c>
       <c r="D83" s="2" t="n"/>
       <c r="E83" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon XK</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>324858338</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>20208000262098074001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №6845</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №178/26, QQS bilan</t>
         </is>
       </c>
       <c r="J83" s="2" t="n">
-        <v>81642000</v>
+        <v>212116000</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="3" t="n">
-        <v>46251</v>
+        <v>46252</v>
       </c>
       <c r="B84" t="n">
         <v>176</v>
       </c>
       <c r="C84" s="2" t="n"/>
       <c r="D84" s="2" t="n">
-        <v>8339000</v>
+        <v>8442000</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -3581,37 +3581,37 @@
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №666 от 17.08.2026, в т.ч. НДС 12%</t>
+          <t>Mahsulot uchun to'lov, shartn. №164/26, QQS 12%</t>
         </is>
       </c>
       <c r="J84" s="2" t="n">
-        <v>89981000</v>
+        <v>220558000</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B85" t="n">
         <v>177</v>
       </c>
       <c r="C85" s="2" t="n"/>
       <c r="D85" s="2" t="n">
-        <v>4158000</v>
+        <v>6110000</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -3621,91 +3621,91 @@
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>Shartnoma №185/26 bo'yicha oldindan to'lov</t>
+          <t>TOVAR UCHUN TO'LOV, H/F №7923 19.08.2026, QQS BILAN</t>
         </is>
       </c>
       <c r="J85" s="2" t="n">
-        <v>94139000</v>
+        <v>226668000</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="3" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="B86" t="n">
         <v>178</v>
       </c>
-      <c r="C86" s="2" t="n">
-        <v>26368000</v>
-      </c>
-      <c r="D86" s="2" t="n"/>
+      <c r="C86" s="2" t="n"/>
+      <c r="D86" s="2" t="n">
+        <v>3054000</v>
+      </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по дог. №64/26</t>
+          <t>Оплата за продукцию по договору №90/26, НДС 12%</t>
         </is>
       </c>
       <c r="J86" s="2" t="n">
-        <v>67771000</v>
+        <v>229722000</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="3" t="n">
-        <v>46253</v>
+        <v>46254</v>
       </c>
       <c r="B87" t="n">
         <v>179</v>
       </c>
       <c r="C87" s="2" t="n"/>
       <c r="D87" s="2" t="n">
-        <v>21494000</v>
+        <v>23540000</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>Shahrisabz Qurilish Materiallari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>290625514</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>20208000216803594001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №257/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9582 20.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J87" s="2" t="n">
-        <v>89265000</v>
+        <v>253262000</v>
       </c>
     </row>
     <row r="88">
@@ -3715,157 +3715,157 @@
       <c r="B88" t="n">
         <v>180</v>
       </c>
-      <c r="C88" s="2" t="n"/>
-      <c r="D88" s="2" t="n">
-        <v>20457000</v>
-      </c>
+      <c r="C88" s="2" t="n">
+        <v>29923000</v>
+      </c>
+      <c r="D88" s="2" t="n"/>
       <c r="E88" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Qo'qon Savdo MChJ</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>270913111</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000715704672001</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №280/26, НДС 12%</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №205/26</t>
         </is>
       </c>
       <c r="J88" s="2" t="n">
-        <v>109722000</v>
+        <v>223339000</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="n">
-        <v>46254</v>
+        <v>46255</v>
       </c>
       <c r="B89" t="n">
         <v>181</v>
       </c>
-      <c r="C89" s="2" t="n"/>
-      <c r="D89" s="2" t="n">
-        <v>6567000</v>
-      </c>
+      <c r="C89" s="2" t="n">
+        <v>5694000</v>
+      </c>
+      <c r="D89" s="2" t="n"/>
       <c r="E89" t="inlineStr">
         <is>
-          <t>Chust Mebel AJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>376006589</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>20208000497660944001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>Shartnoma №19/26 bo'yicha oldindan to'lov</t>
+          <t>Qo'shilgan qiymat solig'i iyul oyi</t>
         </is>
       </c>
       <c r="J89" s="2" t="n">
-        <v>116289000</v>
+        <v>217645000</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B90" t="n">
         <v>182</v>
       </c>
       <c r="C90" s="2" t="n"/>
       <c r="D90" s="2" t="n">
-        <v>38894000</v>
+        <v>11516000</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №224/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7362</t>
         </is>
       </c>
       <c r="J90" s="2" t="n">
-        <v>155183000</v>
+        <v>229161000</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="3" t="n">
-        <v>46255</v>
+        <v>46258</v>
       </c>
       <c r="B91" t="n">
         <v>183</v>
       </c>
       <c r="C91" s="2" t="n"/>
       <c r="D91" s="2" t="n">
-        <v>12374000</v>
+        <v>9477000</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>Yangi Hayot Moy MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>355987668</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>20208000904993031001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №242/26, НДС 12%</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №7051</t>
         </is>
       </c>
       <c r="J91" s="2" t="n">
-        <v>167557000</v>
+        <v>238638000</v>
       </c>
     </row>
     <row r="92">
@@ -3875,23 +3875,23 @@
       <c r="B92" t="n">
         <v>184</v>
       </c>
-      <c r="C92" s="2" t="n"/>
-      <c r="D92" s="2" t="n">
-        <v>30044000</v>
-      </c>
+      <c r="C92" s="2" t="n">
+        <v>3722000</v>
+      </c>
+      <c r="D92" s="2" t="n"/>
       <c r="E92" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
@@ -3901,11 +3901,11 @@
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №957</t>
+          <t>TRANSPORT XIZMATLARI UCHUN TO'LOV, SHARTN. №172/26</t>
         </is>
       </c>
       <c r="J92" s="2" t="n">
-        <v>197601000</v>
+        <v>234916000</v>
       </c>
     </row>
     <row r="93">
@@ -3915,42 +3915,42 @@
       <c r="B93" t="n">
         <v>185</v>
       </c>
-      <c r="C93" s="2" t="n"/>
-      <c r="D93" s="2" t="n">
-        <v>20259000</v>
-      </c>
+      <c r="C93" s="2" t="n">
+        <v>5341000</v>
+      </c>
+      <c r="D93" s="2" t="n"/>
       <c r="E93" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>Оплата за товар по с/ф №2479 от 24.08.2026, в т.ч. НДС 12%</t>
+          <t>Оплата за транспортные услуги по договору №259/26</t>
         </is>
       </c>
       <c r="J93" s="2" t="n">
-        <v>217860000</v>
+        <v>229575000</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B94" t="n">
         <v>186</v>
@@ -3971,181 +3971,181 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>20208000028978953001</t>
+          <t>20208000941079278001</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01153</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Elektr energiyasi uchun to'lov avgust</t>
         </is>
       </c>
       <c r="J94" s="2" t="n">
-        <v>215674000</v>
+        <v>227389000</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="3" t="n">
-        <v>46258</v>
+        <v>46259</v>
       </c>
       <c r="B95" t="n">
         <v>187</v>
       </c>
       <c r="C95" s="2" t="n">
-        <v>5870000</v>
+        <v>4403000</v>
       </c>
       <c r="D95" s="2" t="n"/>
       <c r="E95" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Saodat Metall MChJ</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>204023835</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000536219768001</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>Уплата налога на добавленную стоимость за июль</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №154/26, QQS bilan</t>
         </is>
       </c>
       <c r="J95" s="2" t="n">
-        <v>209804000</v>
+        <v>222986000</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="3" t="n">
-        <v>46259</v>
+        <v>46260</v>
       </c>
       <c r="B96" t="n">
         <v>188</v>
       </c>
       <c r="C96" s="2" t="n"/>
       <c r="D96" s="2" t="n">
-        <v>27919000</v>
+        <v>7097000</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>Chust Mebel AJ</t>
+          <t>Bahor Logistik AJ</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>376006589</t>
+          <t>262551432</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>20208000497660944001</t>
+          <t>20208000680359481001</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №78/26 от 25.08.2026</t>
+          <t>Mahsulot uchun to'lov, shartn. №165/26, QQS 12%</t>
         </is>
       </c>
       <c r="J96" s="2" t="n">
-        <v>237723000</v>
+        <v>230083000</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="3" t="n">
-        <v>46259</v>
+        <v>46261</v>
       </c>
       <c r="B97" t="n">
         <v>189</v>
       </c>
       <c r="C97" s="2" t="n"/>
       <c r="D97" s="2" t="n">
-        <v>19430000</v>
+        <v>11081000</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>Shartnoma №257/26 bo'yicha oldindan to'lov</t>
+          <t>SHARTNOMA №44/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J97" s="2" t="n">
-        <v>257153000</v>
+        <v>241164000</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="3" t="n">
-        <v>46260</v>
+        <v>46261</v>
       </c>
       <c r="B98" t="n">
         <v>190</v>
       </c>
       <c r="C98" s="2" t="n"/>
       <c r="D98" s="2" t="n">
-        <v>18416000</v>
+        <v>4961000</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>398766839</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000499303116001</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №219/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №806 27.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J98" s="2" t="n">
-        <v>275569000</v>
+        <v>246125000</v>
       </c>
     </row>
     <row r="99">
@@ -4157,176 +4157,181 @@
       </c>
       <c r="C99" s="2" t="n"/>
       <c r="D99" s="2" t="n">
-        <v>9863000</v>
+        <v>4455000</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №229/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №6587 27.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J99" s="2" t="n">
-        <v>285432000</v>
+        <v>250580000</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B100" t="n">
         <v>192</v>
       </c>
       <c r="C100" s="2" t="n"/>
       <c r="D100" s="2" t="n">
-        <v>7066000</v>
+        <v>45993000</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4749 за поставленный товар</t>
+          <t>Shartnoma №289/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J100" s="2" t="n">
-        <v>292498000</v>
+        <v>296573000</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="3" t="n">
-        <v>46261</v>
+        <v>46262</v>
       </c>
       <c r="B101" t="n">
         <v>193</v>
       </c>
       <c r="C101" s="2" t="n"/>
       <c r="D101" s="2" t="n">
-        <v>5628000</v>
+        <v>12835000</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Bahor Logistik AJ</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>262551432</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000680359481001</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №4832 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №144 28.08.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J101" s="2" t="n">
-        <v>298126000</v>
+        <v>309408000</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="3" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B102" t="n">
         <v>194</v>
       </c>
-      <c r="C102" s="2" t="n"/>
-      <c r="D102" s="2" t="n">
-        <v>14393000</v>
-      </c>
+      <c r="C102" s="2" t="n">
+        <v>3979000</v>
+      </c>
+      <c r="D102" s="2" t="n"/>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Chust Mebel AJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>376006589</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>20208000497660944001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №6611</t>
+          <t>Tovarlar uchun to'lov h/f №8144</t>
         </is>
       </c>
       <c r="J102" s="2" t="n">
-        <v>312519000</v>
+        <v>305429000</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="3" t="n">
-        <v>46265</v>
+        <v>46262</v>
       </c>
       <c r="B103" t="n">
         <v>195</v>
       </c>
       <c r="C103" s="2" t="n">
-        <v>300000</v>
+        <v>23884000</v>
       </c>
       <c r="D103" s="2" t="n"/>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Bahor Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -4336,11 +4341,11 @@
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>Комиссия за перевод</t>
+          <t>Materiallar uchun oldindan to'lov, shartnoma №156/26</t>
         </is>
       </c>
       <c r="J103" s="2" t="n">
-        <v>312219000</v>
+        <v>281545000</v>
       </c>
     </row>
     <row r="104">
@@ -4350,63 +4355,63 @@
       <c r="B104" t="n">
         <v>196</v>
       </c>
-      <c r="C104" s="2" t="n">
-        <v>30572000</v>
-      </c>
-      <c r="D104" s="2" t="n"/>
+      <c r="C104" s="2" t="n"/>
+      <c r="D104" s="2" t="n">
+        <v>7011000</v>
+      </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №111/26</t>
+          <t>Shartnoma №137/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J104" s="2" t="n">
-        <v>281647000</v>
+        <v>288556000</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="3" t="n">
-        <v>46266</v>
+        <v>46265</v>
       </c>
       <c r="B105" t="n">
         <v>197</v>
       </c>
       <c r="C105" s="2" t="n"/>
       <c r="D105" s="2" t="n">
-        <v>16692000</v>
+        <v>2709000</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -4416,77 +4421,72 @@
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №2731 01.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №158/26, QQS 12%</t>
         </is>
       </c>
       <c r="J105" s="2" t="n">
-        <v>298339000</v>
+        <v>291265000</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="3" t="n">
-        <v>46268</v>
+        <v>46265</v>
       </c>
       <c r="B106" t="n">
         <v>198</v>
       </c>
       <c r="C106" s="2" t="n">
-        <v>17595000</v>
+        <v>300000</v>
       </c>
       <c r="D106" s="2" t="n"/>
       <c r="E106" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon XK</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>324858338</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>20208000262098074001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №275/26 от 03.09.2026, НДС 12%</t>
+          <t>Bank xizmati uchun komissiya</t>
         </is>
       </c>
       <c r="J106" s="2" t="n">
-        <v>280744000</v>
+        <v>290965000</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="3" t="n">
-        <v>46269</v>
+        <v>46268</v>
       </c>
       <c r="B107" t="n">
         <v>199</v>
       </c>
-      <c r="C107" s="2" t="n">
-        <v>101803000</v>
-      </c>
-      <c r="D107" s="2" t="n"/>
+      <c r="C107" s="2" t="n"/>
+      <c r="D107" s="2" t="n">
+        <v>24078000</v>
+      </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Samarqand Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>346550012</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>20208000972500892001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4496,51 +4496,51 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №216/26</t>
+          <t>Mahsulot uchun to'lov, shartnoma №29/26, QQS 12%</t>
         </is>
       </c>
       <c r="J107" s="2" t="n">
-        <v>178941000</v>
+        <v>315043000</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="3" t="n">
-        <v>46272</v>
+        <v>46268</v>
       </c>
       <c r="B108" t="n">
         <v>200</v>
       </c>
       <c r="C108" s="2" t="n"/>
       <c r="D108" s="2" t="n">
-        <v>110947000</v>
+        <v>5338000</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Olmaliq Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>285833812</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>20208000209807425001</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, h/f №5744 07.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartn. №48/26, QQS 12%</t>
         </is>
       </c>
       <c r="J108" s="2" t="n">
-        <v>289888000</v>
+        <v>320381000</v>
       </c>
     </row>
     <row r="109">
@@ -4552,35 +4552,35 @@
       </c>
       <c r="C109" s="2" t="n"/>
       <c r="D109" s="2" t="n">
-        <v>9446000</v>
+        <v>9762000</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Bahor Logistik AJ</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>262551432</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000680359481001</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №8756</t>
+          <t>Mahsulot uchun to'lov, shartnoma №128/26, QQS 12%</t>
         </is>
       </c>
       <c r="J109" s="2" t="n">
-        <v>299334000</v>
+        <v>330143000</v>
       </c>
     </row>
     <row r="110">
@@ -4592,35 +4592,35 @@
       </c>
       <c r="C110" s="2" t="n"/>
       <c r="D110" s="2" t="n">
-        <v>7874000</v>
+        <v>6183000</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №107/26 от 07.09.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №3434 07.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J110" s="2" t="n">
-        <v>307208000</v>
+        <v>336326000</v>
       </c>
     </row>
     <row r="111">
@@ -4630,37 +4630,37 @@
       <c r="B111" t="n">
         <v>203</v>
       </c>
-      <c r="C111" s="2" t="n">
-        <v>5563000</v>
-      </c>
-      <c r="D111" s="2" t="n"/>
+      <c r="C111" s="2" t="n"/>
+      <c r="D111" s="2" t="n">
+        <v>6108000</v>
+      </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>Xiva Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>309434329</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>20208000679295868001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №5/26</t>
+          <t>Shartnoma №238/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J111" s="2" t="n">
-        <v>301645000</v>
+        <v>342434000</v>
       </c>
     </row>
     <row r="112">
@@ -4671,71 +4671,71 @@
         <v>204</v>
       </c>
       <c r="C112" s="2" t="n">
-        <v>35013000</v>
+        <v>15957000</v>
       </c>
       <c r="D112" s="2" t="n"/>
       <c r="E112" t="inlineStr">
         <is>
-          <t>Yangi Asr Bank</t>
+          <t>Saodat Metall MChJ</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>204023835</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>45994000900000001001</t>
+          <t>20208000536219768001</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>Перечисление заработной платы за август 2026 г. согласно реестру №6198</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №154/26</t>
         </is>
       </c>
       <c r="J112" s="2" t="n">
-        <v>266632000</v>
+        <v>326477000</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="n">
-        <v>46273</v>
+        <v>46272</v>
       </c>
       <c r="B113" t="n">
         <v>205</v>
       </c>
-      <c r="C113" s="2" t="n"/>
-      <c r="D113" s="2" t="n">
-        <v>29422000</v>
-      </c>
+      <c r="C113" s="2" t="n">
+        <v>35013000</v>
+      </c>
+      <c r="D113" s="2" t="n"/>
       <c r="E113" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>321535702</t>
+          <t>Yangi Asr Bank</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>45994000900000001001</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №272/26 от 08.09.2026</t>
+          <t>Ish haqi to'lovi avgust 2026 (plastik kartalarga)</t>
         </is>
       </c>
       <c r="J113" s="2" t="n">
-        <v>296054000</v>
+        <v>291464000</v>
       </c>
     </row>
     <row r="114">
@@ -4745,143 +4745,143 @@
       <c r="B114" t="n">
         <v>206</v>
       </c>
-      <c r="C114" s="2" t="n">
-        <v>3666000</v>
-      </c>
-      <c r="D114" s="2" t="n"/>
+      <c r="C114" s="2" t="n"/>
+      <c r="D114" s="2" t="n">
+        <v>33649000</v>
+      </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>Urganch Qurilish Materiallari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>279508176</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>20208000985398076001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>IJARA HAQI SENTYABR OYI UCHUN, SHARTNOMA №77/21</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №1695</t>
         </is>
       </c>
       <c r="J114" s="2" t="n">
-        <v>292388000</v>
+        <v>325113000</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="3" t="n">
-        <v>46274</v>
+        <v>46273</v>
       </c>
       <c r="B115" t="n">
         <v>207</v>
       </c>
-      <c r="C115" s="2" t="n">
-        <v>48028000</v>
-      </c>
-      <c r="D115" s="2" t="n"/>
+      <c r="C115" s="2" t="n"/>
+      <c r="D115" s="2" t="n">
+        <v>20767000</v>
+      </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Shodlik Tur Servis MChJ</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>389710340</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000764134970001</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>00962</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №111/26 от 09.09.2026, НДС 12%</t>
+          <t>Shartnoma №12/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J115" s="2" t="n">
-        <v>244360000</v>
+        <v>345880000</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="3" t="n">
-        <v>46275</v>
+        <v>46273</v>
       </c>
       <c r="B116" t="n">
         <v>208</v>
       </c>
       <c r="C116" s="2" t="n"/>
       <c r="D116" s="2" t="n">
-        <v>12016000</v>
+        <v>18576000</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по договору №278/26, НДС 12%</t>
+          <t>Tovar uchun to'lov, h/f №7517 08.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J116" s="2" t="n">
-        <v>256376000</v>
+        <v>364456000</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="3" t="n">
-        <v>46275</v>
+        <v>46273</v>
       </c>
       <c r="B117" t="n">
         <v>209</v>
       </c>
       <c r="C117" s="2" t="n">
-        <v>16662000</v>
+        <v>3666000</v>
       </c>
       <c r="D117" s="2" t="n"/>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Samarqand Sut Mahsulotlari MChJ</t>
+          <t>Marg'ilon Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>346550012</t>
+          <t>294343295</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>20208000972500892001</t>
+          <t>20208000792958688001</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4891,32 +4891,37 @@
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №1501</t>
+          <t>Аренда помещения за сентябрь, дог. №41/20</t>
         </is>
       </c>
       <c r="J117" s="2" t="n">
-        <v>239714000</v>
+        <v>360790000</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="3" t="n">
-        <v>46275</v>
+        <v>46274</v>
       </c>
       <c r="B118" t="n">
         <v>210</v>
       </c>
-      <c r="C118" s="2" t="n">
-        <v>66600000</v>
-      </c>
-      <c r="D118" s="2" t="n"/>
+      <c r="C118" s="2" t="n"/>
+      <c r="D118" s="2" t="n">
+        <v>25908000</v>
+      </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>Kreditni qaytarish hisobvarag'i (L-2024-4382)</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>16307000371475974417</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -4926,237 +4931,232 @@
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>Kredit shartnomasi L-2024-4382 bo'yicha navbatdagi to'lov (09.2026)</t>
+          <t>Оплата по с/ф №4364 за поставленный товар</t>
         </is>
       </c>
       <c r="J118" s="2" t="n">
-        <v>173114000</v>
+        <v>386698000</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="3" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="B119" t="n">
         <v>211</v>
       </c>
-      <c r="C119" s="2" t="n">
-        <v>4774000</v>
-      </c>
-      <c r="D119" s="2" t="n"/>
+      <c r="C119" s="2" t="n"/>
+      <c r="D119" s="2" t="n">
+        <v>6922000</v>
+      </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>Уплата социального налога за август</t>
+          <t>Оплата по счет-фактуре №8611 за поставленный товар</t>
         </is>
       </c>
       <c r="J119" s="2" t="n">
-        <v>168340000</v>
+        <v>393620000</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="3" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="B120" t="n">
         <v>212</v>
       </c>
       <c r="C120" s="2" t="n">
-        <v>4774000</v>
+        <v>38734000</v>
       </c>
       <c r="D120" s="2" t="n"/>
       <c r="E120" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Qo'qon Savdo MChJ</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>270913111</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000715704672001</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>Налог на доходы физических лиц за август 2026 г.</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №195/26</t>
         </is>
       </c>
       <c r="J120" s="2" t="n">
-        <v>163566000</v>
+        <v>354886000</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="3" t="n">
-        <v>46279</v>
+        <v>46275</v>
       </c>
       <c r="B121" t="n">
         <v>213</v>
       </c>
       <c r="C121" s="2" t="n">
-        <v>5393000</v>
+        <v>66600000</v>
       </c>
       <c r="D121" s="2" t="n"/>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>228897103</t>
+          <t>Kreditni qaytarish hisobvarag'i (L-2024-4382)</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>16307000371475974417</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
         <is>
-          <t>ПРЕДОПЛАТА ЗА МАТЕРИАЛЫ ПО ДОГОВОРУ №71/26</t>
+          <t>Kredit shartnomasi L-2024-4382 bo'yicha navbatdagi to'lov (09.2026)</t>
         </is>
       </c>
       <c r="J121" s="2" t="n">
-        <v>158173000</v>
+        <v>288286000</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B122" t="n">
         <v>214</v>
       </c>
       <c r="C122" s="2" t="n"/>
       <c r="D122" s="2" t="n">
-        <v>5983000</v>
+        <v>30033000</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Olmaliq Meva-Sabzavot MChJ</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>285833812</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000209807425001</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №178/26 от 15.09.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №9281 14.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J122" s="2" t="n">
-        <v>164156000</v>
+        <v>318319000</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B123" t="n">
         <v>215</v>
       </c>
-      <c r="C123" s="2" t="n">
-        <v>6479000</v>
-      </c>
-      <c r="D123" s="2" t="n"/>
+      <c r="C123" s="2" t="n"/>
+      <c r="D123" s="2" t="n">
+        <v>16872000</v>
+      </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>Оплата за транспортные услуги по договору №278/26</t>
+          <t>Предоплата за товар по договору №215/26 от 14.09.2026</t>
         </is>
       </c>
       <c r="J123" s="2" t="n">
-        <v>157677000</v>
+        <v>335191000</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="3" t="n">
-        <v>46280</v>
+        <v>46279</v>
       </c>
       <c r="B124" t="n">
         <v>216</v>
       </c>
-      <c r="C124" s="2" t="n">
-        <v>40476000</v>
-      </c>
-      <c r="D124" s="2" t="n"/>
+      <c r="C124" s="2" t="n"/>
+      <c r="D124" s="2" t="n">
+        <v>10233000</v>
+      </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Samarqand Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>346550012</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>20208000972500892001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
@@ -5166,117 +5166,117 @@
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №8157</t>
+          <t>Yetkazilgan tovar uchun to'lov h/f №9704</t>
         </is>
       </c>
       <c r="J124" s="2" t="n">
-        <v>117201000</v>
+        <v>345424000</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="3" t="n">
-        <v>46281</v>
+        <v>46279</v>
       </c>
       <c r="B125" t="n">
         <v>217</v>
       </c>
       <c r="C125" s="2" t="n"/>
       <c r="D125" s="2" t="n">
-        <v>19918000</v>
+        <v>8762000</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>Tovar uchun to'lov, hisob-faktura №4686 16.09.2026, QQS bilan</t>
+          <t>Mahsulot uchun to'lov, shartnoma №295/26, QQS 12%</t>
         </is>
       </c>
       <c r="J125" s="2" t="n">
-        <v>137119000</v>
+        <v>354186000</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="3" t="n">
-        <v>46282</v>
+        <v>46279</v>
       </c>
       <c r="B126" t="n">
         <v>218</v>
       </c>
-      <c r="C126" s="2" t="n">
-        <v>4635000</v>
-      </c>
-      <c r="D126" s="2" t="n"/>
+      <c r="C126" s="2" t="n"/>
+      <c r="D126" s="2" t="n">
+        <v>8167000</v>
+      </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>398766839</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000499303116001</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №264/26 от 17.09.2026, НДС 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №4664 14.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J126" s="2" t="n">
-        <v>132484000</v>
+        <v>362353000</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="3" t="n">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="B127" t="n">
         <v>219</v>
       </c>
-      <c r="C127" s="2" t="n">
-        <v>16471000</v>
-      </c>
-      <c r="D127" s="2" t="n"/>
+      <c r="C127" s="2" t="n"/>
+      <c r="D127" s="2" t="n">
+        <v>28592000</v>
+      </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>Samarqand Sut Mahsulotlari MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>346550012</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>20208000972500892001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
@@ -5286,211 +5286,211 @@
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №64/26</t>
+          <t>Оплата за продукцию по договору №28/26, НДС 12%</t>
         </is>
       </c>
       <c r="J127" s="2" t="n">
-        <v>116013000</v>
+        <v>390945000</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="3" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B128" t="n">
         <v>220</v>
       </c>
       <c r="C128" s="2" t="n"/>
       <c r="D128" s="2" t="n">
-        <v>32561000</v>
+        <v>19697000</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>Предоплата за твар по дог. №72/26 от 18.09.2026</t>
+          <t>Shartnoma №93/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J128" s="2" t="n">
-        <v>148574000</v>
+        <v>410642000</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="3" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B129" t="n">
         <v>221</v>
       </c>
-      <c r="C129" s="2" t="n"/>
-      <c r="D129" s="2" t="n">
-        <v>30121000</v>
-      </c>
+      <c r="C129" s="2" t="n">
+        <v>4774000</v>
+      </c>
+      <c r="D129" s="2" t="n"/>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №8771 за поставленный товар</t>
+          <t>Ijtimoiy soliq avgust 2026</t>
         </is>
       </c>
       <c r="J129" s="2" t="n">
-        <v>178695000</v>
+        <v>405868000</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="3" t="n">
-        <v>46283</v>
+        <v>46280</v>
       </c>
       <c r="B130" t="n">
         <v>222</v>
       </c>
-      <c r="C130" s="2" t="n"/>
-      <c r="D130" s="2" t="n">
-        <v>8479000</v>
-      </c>
+      <c r="C130" s="2" t="n">
+        <v>4774000</v>
+      </c>
+      <c r="D130" s="2" t="n"/>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Durdona Oziq-ovqat Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>206716469</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>20208000779434172001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>01089</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №107/26 от 18.09.2026</t>
+          <t>Jismoniy shaxslar daromad solig'i avgust 2026</t>
         </is>
       </c>
       <c r="J130" s="2" t="n">
-        <v>187174000</v>
+        <v>401094000</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="3" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="B131" t="n">
         <v>223</v>
       </c>
       <c r="C131" s="2" t="n"/>
       <c r="D131" s="2" t="n">
-        <v>42322000</v>
+        <v>7156000</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №92/26 от 21.09.2026</t>
+          <t>Tovar uchun to'lov, hisob-faktura №403 18.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J131" s="2" t="n">
-        <v>229496000</v>
+        <v>408250000</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="3" t="n">
-        <v>46286</v>
+        <v>46283</v>
       </c>
       <c r="B132" t="n">
         <v>224</v>
       </c>
-      <c r="C132" s="2" t="n"/>
-      <c r="D132" s="2" t="n">
-        <v>20095000</v>
-      </c>
+      <c r="C132" s="2" t="n">
+        <v>75517000</v>
+      </c>
+      <c r="D132" s="2" t="n"/>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Chust Mebel AJ</t>
+          <t>Urganch Moy MChJ</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>376006589</t>
+          <t>380892181</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>20208000497660944001</t>
+          <t>20208000223286429001</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>Оплата за продукцию по дог. №211/26, НДС 12%</t>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №261/26</t>
         </is>
       </c>
       <c r="J132" s="2" t="n">
-        <v>249591000</v>
+        <v>332733000</v>
       </c>
     </row>
     <row r="133">
@@ -5502,35 +5502,35 @@
       </c>
       <c r="C133" s="2" t="n"/>
       <c r="D133" s="2" t="n">
-        <v>6620000</v>
+        <v>17250000</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>Оплата по с/ф №2441 за поставленный товар</t>
+          <t>Tovar uchun to'lov, hisob-faktura №2640 21.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J133" s="2" t="n">
-        <v>256211000</v>
+        <v>349983000</v>
       </c>
     </row>
     <row r="134">
@@ -5540,37 +5540,37 @@
       <c r="B134" t="n">
         <v>226</v>
       </c>
-      <c r="C134" s="2" t="n">
-        <v>4259000</v>
-      </c>
-      <c r="D134" s="2" t="n"/>
+      <c r="C134" s="2" t="n"/>
+      <c r="D134" s="2" t="n">
+        <v>8013000</v>
+      </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>Yulduz Un Mahsulotlari MChJ</t>
+          <t>Farg'ona Avto Ehtiyot MChJ</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>228897103</t>
+          <t>371646977</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>20208000087641349001</t>
+          <t>20208000943417238001</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>00987</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>Transport xizmatlari uchun to'lov, shartnoma №266/26</t>
+          <t>Предоплата за товар по договору №180/26 от 21.09.2026</t>
         </is>
       </c>
       <c r="J134" s="2" t="n">
-        <v>251952000</v>
+        <v>357996000</v>
       </c>
     </row>
     <row r="135">
@@ -5580,37 +5580,37 @@
       <c r="B135" t="n">
         <v>227</v>
       </c>
-      <c r="C135" s="2" t="n">
-        <v>6281000</v>
-      </c>
-      <c r="D135" s="2" t="n"/>
+      <c r="C135" s="2" t="n"/>
+      <c r="D135" s="2" t="n">
+        <v>5332000</v>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>201122905</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>23402000300100001010</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>00014</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>НДС за август 2026 г.</t>
+          <t>SHARTNOMA №202/26 BO'YICHA OLDINDAN TO'LOV</t>
         </is>
       </c>
       <c r="J135" s="2" t="n">
-        <v>245671000</v>
+        <v>363328000</v>
       </c>
     </row>
     <row r="136">
@@ -5621,382 +5621,382 @@
         <v>228</v>
       </c>
       <c r="C136" s="2" t="n">
-        <v>10952000</v>
+        <v>15337000</v>
       </c>
       <c r="D136" s="2" t="n"/>
       <c r="E136" t="inlineStr">
         <is>
-          <t>Olmaliq Qurilish Materiallari XK</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>335808921</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>20208000102232864001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>Оплата за товары согласно с/ф №958</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №209/26, QQS bilan</t>
         </is>
       </c>
       <c r="J136" s="2" t="n">
-        <v>234719000</v>
+        <v>347991000</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="3" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="B137" t="n">
         <v>229</v>
       </c>
       <c r="C137" s="2" t="n">
-        <v>20043000</v>
+        <v>24951000</v>
       </c>
       <c r="D137" s="2" t="n"/>
       <c r="E137" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon XK</t>
+          <t>Saodat Metall MChJ</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>324858338</t>
+          <t>204023835</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>20208000262098074001</t>
+          <t>20208000536219768001</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>Оплата за сырье по договору №116/26 от 23.09.2026, НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №4160</t>
         </is>
       </c>
       <c r="J137" s="2" t="n">
-        <v>214676000</v>
+        <v>323040000</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" s="3" t="n">
-        <v>46289</v>
+        <v>46286</v>
       </c>
       <c r="B138" t="n">
         <v>230</v>
       </c>
       <c r="C138" s="2" t="n">
-        <v>81109000</v>
+        <v>33677000</v>
       </c>
       <c r="D138" s="2" t="n"/>
       <c r="E138" t="inlineStr">
         <is>
-          <t>Farovon Dori-Darmon XK</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>324858338</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>20208000262098074001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
         <is>
-          <t>Оплата за упаковочные материалы, с/ф №165</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №247/26, QQS bilan</t>
         </is>
       </c>
       <c r="J138" s="2" t="n">
-        <v>133567000</v>
+        <v>289363000</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="3" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="B139" t="n">
         <v>231</v>
       </c>
-      <c r="C139" s="2" t="n"/>
-      <c r="D139" s="2" t="n">
-        <v>108883000</v>
-      </c>
+      <c r="C139" s="2" t="n">
+        <v>37283000</v>
+      </c>
+      <c r="D139" s="2" t="n"/>
       <c r="E139" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Urganch Moy MChJ</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>380892181</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000223286429001</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I139" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №1549 от 28.09.2026, в т.ч. НДС 12%</t>
+          <t>Tovarlar uchun to'lov h/f №4500</t>
         </is>
       </c>
       <c r="J139" s="2" t="n">
-        <v>242450000</v>
+        <v>252080000</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B140" t="n">
         <v>232</v>
       </c>
       <c r="C140" s="2" t="n"/>
       <c r="D140" s="2" t="n">
-        <v>20011000</v>
+        <v>8317000</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Oqtosh Trans Servis MChJ</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>398766839</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000499303116001</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01121</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №1579</t>
+          <t>Shartnoma №92/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J140" s="2" t="n">
-        <v>262461000</v>
+        <v>260397000</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" s="3" t="n">
-        <v>46293</v>
+        <v>46287</v>
       </c>
       <c r="B141" t="n">
         <v>233</v>
       </c>
-      <c r="C141" s="2" t="n"/>
-      <c r="D141" s="2" t="n">
-        <v>6698000</v>
-      </c>
+      <c r="C141" s="2" t="n">
+        <v>5977000</v>
+      </c>
+      <c r="D141" s="2" t="n"/>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Davlat soliq qo'mitasi (budjet hisobvarag'i)</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>201122905</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>23402000300100001010</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>00014</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>Оплата по счет-фактуре №9322 за поставленный товар</t>
+          <t>Qo'shilgan qiymat solig'i avgust oyi</t>
         </is>
       </c>
       <c r="J141" s="2" t="n">
-        <v>269159000</v>
+        <v>254420000</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B142" t="n">
         <v>234</v>
       </c>
       <c r="C142" s="2" t="n"/>
       <c r="D142" s="2" t="n">
-        <v>5910000</v>
+        <v>35813000</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>Mahsulot uchun to'lov, shartnoma №274/26, QQS 12%</t>
+          <t>Tovar uchun to'lov, hisob-faktura №5459 23.09.2026, QQS bilan</t>
         </is>
       </c>
       <c r="J142" s="2" t="n">
-        <v>275069000</v>
+        <v>290233000</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" s="3" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="B143" t="n">
         <v>235</v>
       </c>
-      <c r="C143" s="2" t="n">
-        <v>2291000</v>
-      </c>
-      <c r="D143" s="2" t="n"/>
+      <c r="C143" s="2" t="n"/>
+      <c r="D143" s="2" t="n">
+        <v>21913000</v>
+      </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>Hududiy elektr tarmoqlari AJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>200933985</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>20208000028978953001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>01204</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I143" t="inlineStr">
         <is>
-          <t>Оплата за электроэнергию согласно счету</t>
+          <t>Mahsulot uchun to'lov, shartnoma №296/26, QQS 12%</t>
         </is>
       </c>
       <c r="J143" s="2" t="n">
-        <v>272778000</v>
+        <v>312146000</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="3" t="n">
-        <v>46294</v>
+        <v>46288</v>
       </c>
       <c r="B144" t="n">
         <v>236</v>
       </c>
       <c r="C144" s="2" t="n">
-        <v>6438000</v>
+        <v>62094000</v>
       </c>
       <c r="D144" s="2" t="n"/>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Chirchiq Logistik AJ</t>
+          <t>Bahor Mehmonxona MChJ</t>
         </is>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>232709131</t>
+          <t>355001269</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>20208000157157046001</t>
+          <t>20208000250089209001</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>01121</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>Предоплата за материалы по договору №191/26</t>
+          <t>Xom ashyo uchun to'lov, shartnoma №201/26, QS bilan</t>
         </is>
       </c>
       <c r="J144" s="2" t="n">
-        <v>266340000</v>
+        <v>250052000</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="3" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B145" t="n">
         <v>237</v>
       </c>
-      <c r="C145" s="2" t="n"/>
-      <c r="D145" s="2" t="n">
-        <v>12934000</v>
-      </c>
+      <c r="C145" s="2" t="n">
+        <v>2291000</v>
+      </c>
+      <c r="D145" s="2" t="n"/>
       <c r="E145" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Hududiy elektr tarmoqlari AJ</t>
         </is>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>200933985</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000941079278001</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
@@ -6006,91 +6006,91 @@
       </c>
       <c r="I145" t="inlineStr">
         <is>
-          <t>Yetkazilgan tovar uchun to'lov h/f №5368</t>
+          <t>Elektr energiyasi uchun to'lov</t>
         </is>
       </c>
       <c r="J145" s="2" t="n">
-        <v>279274000</v>
+        <v>247761000</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="3" t="n">
-        <v>46295</v>
+        <v>46293</v>
       </c>
       <c r="B146" t="n">
         <v>238</v>
       </c>
-      <c r="C146" s="2" t="n"/>
-      <c r="D146" s="2" t="n">
-        <v>8478000</v>
-      </c>
+      <c r="C146" s="2" t="n">
+        <v>10170000</v>
+      </c>
+      <c r="D146" s="2" t="n"/>
       <c r="E146" t="inlineStr">
         <is>
-          <t>Omad Savdo MChJ</t>
+          <t>Saodat Metall MChJ</t>
         </is>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>321535702</t>
+          <t>204023835</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>20208000281993513001</t>
+          <t>20208000536219768001</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>01153</t>
+          <t>01204</t>
         </is>
       </c>
       <c r="I146" t="inlineStr">
         <is>
-          <t>Предоплата за товар по договору №140/26 от 30.09.2026</t>
+          <t>Tovarlar uchun to'lov h/f №8224</t>
         </is>
       </c>
       <c r="J146" s="2" t="n">
-        <v>287752000</v>
+        <v>237591000</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="3" t="n">
-        <v>46295</v>
+        <v>46294</v>
       </c>
       <c r="B147" t="n">
         <v>239</v>
       </c>
       <c r="C147" s="2" t="n"/>
       <c r="D147" s="2" t="n">
-        <v>8048000</v>
+        <v>114659000</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Chust Mebel AJ</t>
+          <t>Tong Qurilish Materiallari MChJ</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>376006589</t>
+          <t>253570212</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>20208000497660944001</t>
+          <t>20208000199351322001</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>00962</t>
+          <t>01089</t>
         </is>
       </c>
       <c r="I147" t="inlineStr">
         <is>
-          <t>Оплата за товар по счет-фактуре №2552 от 30.09.2026, в т.ч. НДС 12%</t>
+          <t>Shartnoma №80/26 bo'yicha oldindan to'lov</t>
         </is>
       </c>
       <c r="J147" s="2" t="n">
-        <v>295800000</v>
+        <v>352250000</v>
       </c>
     </row>
     <row r="148">
@@ -6121,36 +6121,116 @@
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>Комиссия банка за расчетно-кассовое обслуживание за сентябрь</t>
+          <t>Плата за SMS-инфомирование</t>
         </is>
       </c>
       <c r="J148" s="2" t="n">
+        <v>351950000</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B149" t="n">
+        <v>241</v>
+      </c>
+      <c r="C149" s="2" t="n">
+        <v>11342000</v>
+      </c>
+      <c r="D149" s="2" t="n"/>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Bahor Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>355001269</t>
+        </is>
+      </c>
+      <c r="G149" t="inlineStr">
+        <is>
+          <t>20208000250089209001</t>
+        </is>
+      </c>
+      <c r="H149" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr">
+        <is>
+          <t>Transport xizmatlari uchun to'lov, shartnoma №86/26</t>
+        </is>
+      </c>
+      <c r="J149" s="2" t="n">
+        <v>340608000</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="3" t="n">
+        <v>46295</v>
+      </c>
+      <c r="B150" t="n">
+        <v>242</v>
+      </c>
+      <c r="C150" s="2" t="n">
+        <v>45108000</v>
+      </c>
+      <c r="D150" s="2" t="n"/>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>Bahor Mehmonxona MChJ</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>355001269</t>
+        </is>
+      </c>
+      <c r="G150" t="inlineStr">
+        <is>
+          <t>20208000250089209001</t>
+        </is>
+      </c>
+      <c r="H150" t="inlineStr">
+        <is>
+          <t>01089</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>Оплата за упаковочные материалы, с/ф №7163</t>
+        </is>
+      </c>
+      <c r="J150" s="2" t="n">
         <v>295500000</v>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
+    <row r="151">
+      <c r="A151" t="inlineStr">
         <is>
           <t>Итого обороты:</t>
         </is>
       </c>
-      <c r="C149" s="4" t="n">
-        <v>1531389000</v>
-      </c>
-      <c r="D149" s="4" t="n">
-        <v>1544989000</v>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
+      <c r="C151" s="4" t="n">
+        <v>1483517000</v>
+      </c>
+      <c r="D151" s="4" t="n">
+        <v>1497117000</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
         <is>
           <t>Исходящий остаток на 30.09.2026:</t>
         </is>
       </c>
-      <c r="C150" s="4" t="n">
+      <c r="C152" s="4" t="n">
         <v>295500000</v>
       </c>
-      <c r="D150" s="4" t="n"/>
+      <c r="D152" s="4" t="n"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
